--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EDC22E-5154-4A22-985C-F14D880EE963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EFBAFF-0347-44DE-B0E7-84B88CD87A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>10/11/1973</t>
+    <t>10/11/1973 00:00:00</t>
   </si>
   <si>
     <t>Nigéria</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>06/09/2022</t>
-  </si>
-  <si>
-    <t>01/12/2025</t>
+    <t>06/09/2022 00:00:00</t>
+  </si>
+  <si>
+    <t>01/12/2025 00:00:00</t>
   </si>
   <si>
     <t>BARSEGHIAN</t>
@@ -79,7 +79,7 @@
     <t>Norik</t>
   </si>
   <si>
-    <t>07/07/2006</t>
+    <t>07/07/2006 00:00:00</t>
   </si>
   <si>
     <t>Arménie</t>
@@ -88,10 +88,10 @@
     <t>M</t>
   </si>
   <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>11/09/2025 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>CARBONO FERNANDEZ</t>
@@ -103,7 +103,7 @@
     <t>Colombie</t>
   </si>
   <si>
-    <t>16/01/2025</t>
+    <t>16/01/2025 00:00:00</t>
   </si>
   <si>
     <t>CHEGGARI</t>
@@ -112,13 +112,13 @@
     <t>Nour Eddin</t>
   </si>
   <si>
-    <t>23/10/1994</t>
+    <t>23/10/1994 00:00:00</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>31/05/2023</t>
+    <t>31/05/2023 00:00:00</t>
   </si>
   <si>
     <t>HALILAJ</t>
@@ -127,13 +127,13 @@
     <t>Lindita</t>
   </si>
   <si>
-    <t>23/02/1979</t>
+    <t>23/02/1979 00:00:00</t>
   </si>
   <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>09/11/2023</t>
+    <t>09/11/2023 00:00:00</t>
   </si>
   <si>
     <t>KIAKU</t>
@@ -142,13 +142,13 @@
     <t>Ana Marcela</t>
   </si>
   <si>
-    <t>19/02/1992</t>
+    <t>19/02/1992 00:00:00</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>20/09/2023</t>
+    <t>20/09/2023 00:00:00</t>
   </si>
   <si>
     <t>LMABROUK</t>
@@ -157,10 +157,10 @@
     <t>Oussama</t>
   </si>
   <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>01/02/2025</t>
+    <t>01/01/1994 00:00:00</t>
+  </si>
+  <si>
+    <t>01/02/2025 00:00:00</t>
   </si>
   <si>
     <t>MANGAY</t>
@@ -169,13 +169,13 @@
     <t>Paul</t>
   </si>
   <si>
-    <t>25/06/1990</t>
+    <t>25/06/1990 00:00:00</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>16/09/2025</t>
+    <t>16/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MENAYAME NGOMA</t>
@@ -184,10 +184,10 @@
     <t>Mera</t>
   </si>
   <si>
-    <t>05/05/1994</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
+    <t>05/05/1994 00:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2025 00:00:00</t>
   </si>
   <si>
     <t>MUSTAFAYEVA</t>
@@ -196,13 +196,13 @@
     <t>Gulkanim</t>
   </si>
   <si>
-    <t>17/09/1990</t>
+    <t>17/09/1990 00:00:00</t>
   </si>
   <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
-    <t>26/06/2019</t>
+    <t>26/06/2019 00:00:00</t>
   </si>
   <si>
     <t>NYINAWUMUNTU</t>
@@ -214,7 +214,7 @@
     <t>Rwanda</t>
   </si>
   <si>
-    <t>19/09/2024</t>
+    <t>19/09/2024 00:00:00</t>
   </si>
   <si>
     <t>OYEKAN</t>
@@ -223,10 +223,10 @@
     <t>Patrick</t>
   </si>
   <si>
-    <t>17/01/1976</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
+    <t>17/01/1976 00:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2024 00:00:00</t>
   </si>
   <si>
     <t>REYES OTERO</t>
@@ -235,10 +235,10 @@
     <t>Victor Hugo</t>
   </si>
   <si>
-    <t>29/05/1986</t>
-  </si>
-  <si>
-    <t>06/05/2025</t>
+    <t>29/05/1986 00:00:00</t>
+  </si>
+  <si>
+    <t>06/05/2025 00:00:00</t>
   </si>
   <si>
     <t>SAUCEDO  FERNANDEZ</t>
@@ -247,7 +247,7 @@
     <t>Verselia</t>
   </si>
   <si>
-    <t>03/07/1989</t>
+    <t>03/07/1989 00:00:00</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -737,7 +737,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EFBAFF-0347-44DE-B0E7-84B88CD87A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7137E2-EFE8-46B0-A518-B6BCBBDA1DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Elizabeth</t>
   </si>
   <si>
-    <t>10/11/1973 00:00:00</t>
+    <t>10/11/1973</t>
   </si>
   <si>
     <t>Nigéria</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>06/09/2022 00:00:00</t>
-  </si>
-  <si>
-    <t>01/12/2025 00:00:00</t>
+    <t>06/09/2022</t>
+  </si>
+  <si>
+    <t>01/12/2025</t>
   </si>
   <si>
     <t>BARSEGHIAN</t>
@@ -79,7 +79,7 @@
     <t>Norik</t>
   </si>
   <si>
-    <t>07/07/2006 00:00:00</t>
+    <t>07/07/2006</t>
   </si>
   <si>
     <t>Arménie</t>
@@ -88,10 +88,10 @@
     <t>M</t>
   </si>
   <si>
-    <t>11/09/2025 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>CARBONO FERNANDEZ</t>
@@ -103,7 +103,7 @@
     <t>Colombie</t>
   </si>
   <si>
-    <t>16/01/2025 00:00:00</t>
+    <t>16/01/2025</t>
   </si>
   <si>
     <t>CHEGGARI</t>
@@ -112,13 +112,13 @@
     <t>Nour Eddin</t>
   </si>
   <si>
-    <t>23/10/1994 00:00:00</t>
+    <t>23/10/1994</t>
   </si>
   <si>
     <t>Maroc</t>
   </si>
   <si>
-    <t>31/05/2023 00:00:00</t>
+    <t>31/05/2023</t>
   </si>
   <si>
     <t>HALILAJ</t>
@@ -127,13 +127,13 @@
     <t>Lindita</t>
   </si>
   <si>
-    <t>23/02/1979 00:00:00</t>
+    <t>23/02/1979</t>
   </si>
   <si>
     <t>Albanie</t>
   </si>
   <si>
-    <t>09/11/2023 00:00:00</t>
+    <t>09/11/2023</t>
   </si>
   <si>
     <t>KIAKU</t>
@@ -142,13 +142,13 @@
     <t>Ana Marcela</t>
   </si>
   <si>
-    <t>19/02/1992 00:00:00</t>
+    <t>19/02/1992</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>20/09/2023 00:00:00</t>
+    <t>20/09/2023</t>
   </si>
   <si>
     <t>LMABROUK</t>
@@ -157,10 +157,10 @@
     <t>Oussama</t>
   </si>
   <si>
-    <t>01/01/1994 00:00:00</t>
-  </si>
-  <si>
-    <t>01/02/2025 00:00:00</t>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
   </si>
   <si>
     <t>MANGAY</t>
@@ -169,13 +169,13 @@
     <t>Paul</t>
   </si>
   <si>
-    <t>25/06/1990 00:00:00</t>
+    <t>25/06/1990</t>
   </si>
   <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>16/09/2025 00:00:00</t>
+    <t>16/09/2025</t>
   </si>
   <si>
     <t>MENAYAME NGOMA</t>
@@ -184,10 +184,10 @@
     <t>Mera</t>
   </si>
   <si>
-    <t>05/05/1994 00:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2025 00:00:00</t>
+    <t>05/05/1994</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>MUSTAFAYEVA</t>
@@ -196,13 +196,13 @@
     <t>Gulkanim</t>
   </si>
   <si>
-    <t>17/09/1990 00:00:00</t>
+    <t>17/09/1990</t>
   </si>
   <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
-    <t>26/06/2019 00:00:00</t>
+    <t>26/06/2019</t>
   </si>
   <si>
     <t>NYINAWUMUNTU</t>
@@ -214,7 +214,7 @@
     <t>Rwanda</t>
   </si>
   <si>
-    <t>19/09/2024 00:00:00</t>
+    <t>19/09/2024</t>
   </si>
   <si>
     <t>OYEKAN</t>
@@ -223,10 +223,10 @@
     <t>Patrick</t>
   </si>
   <si>
-    <t>17/01/1976 00:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2024 00:00:00</t>
+    <t>17/01/1976</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
   </si>
   <si>
     <t>REYES OTERO</t>
@@ -235,10 +235,10 @@
     <t>Victor Hugo</t>
   </si>
   <si>
-    <t>29/05/1986 00:00:00</t>
-  </si>
-  <si>
-    <t>06/05/2025 00:00:00</t>
+    <t>29/05/1986</t>
+  </si>
+  <si>
+    <t>06/05/2025</t>
   </si>
   <si>
     <t>SAUCEDO  FERNANDEZ</t>
@@ -247,7 +247,7 @@
     <t>Verselia</t>
   </si>
   <si>
-    <t>03/07/1989 00:00:00</t>
+    <t>03/07/1989</t>
   </si>
   <si>
     <t>Pérou</t>
@@ -737,7 +737,7 @@
     <col min="5" max="5" width="33" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7137E2-EFE8-46B0-A518-B6BCBBDA1DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC94B5E5-BB2F-421C-8067-9D349EACACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC94B5E5-BB2F-421C-8067-9D349EACACF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBAE5B1-2D8D-4728-BC71-EE7CAC4BB0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBAE5B1-2D8D-4728-BC71-EE7CAC4BB0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB141C51-9633-4960-9175-B328A413A95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_5.xlsx
+++ b/Excel/liste_groupe_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB141C51-9633-4960-9175-B328A413A95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD88F4A8-2184-4A89-928D-ECBBE2F8ABB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
